--- a/docs/balanceamento.xlsx
+++ b/docs/balanceamento.xlsx
@@ -327,7 +327,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não ataca. Segura 1 inimigo na rota e causa 11 de dano por segundo de contato em quem está preso.</t>
+          <t xml:space="preserve">Não ataca. Segura 1 inimigo por 3,5s e causa 11/s de contato. V3.1: o agarrão deixou de ser PERMANENTE — depois de soltar, 1,5s até poder pegar o mesmo de novo.</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plataforma</t>
+          <t xml:space="preserve">Plataforma ou água</t>
         </is>
       </c>
       <c r="E6">
@@ -548,18 +548,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Não (só com o ramo A)</t>
+          <t xml:space="preserve">Sim</t>
         </is>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A batida deixa o alvo a 75% da velocidade por 1,4s. O valor dela é o controle. V3: dano 8 → 11.</t>
+          <t xml:space="preserve">V3.1: bloqueia desde a base — 2 inimigos por 3s. A batida deixa o alvo a 75% da velocidade por 1,4s.</t>
         </is>
       </c>
     </row>
@@ -594,10 +594,10 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enterra-se em 2,6s e explode em quem pisar no raio 65: 40 de dano, recarga 5s. Cada 2s armado soma +6% de dano (teto +36% = 54,4).</t>
+          <t xml:space="preserve">V3.1: NÃO dispara no primeiro contato. Enterra-se em 2,6s e espera o grupo se formar, saindo pouco antes de o primeiro escapar do raio 65 (a 53 px dela) — o instante com mais gente dentro. 40 de dano, recarga 2,5s (era 5s). Cada 2s armado soma +6% (teto +36% = 54,4).</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Água livre</t>
+          <t xml:space="preserve">Água livre ou margem</t>
         </is>
       </c>
       <c r="E10">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segura 3 inimigos ao mesmo tempo e o contato sobe para 15 de dano por segundo em CADA um preso (45/s com a lotação cheia).</t>
+          <t xml:space="preserve">Segura 3 inimigos por 4,5s cada e o contato sobe para 15/s em CADA um preso (45/s com a lotação cheia). Recarga de 1,5s por inimigo solto.</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segura 5 inimigos, 19 de dano/s em cada um (95/s lotado). Também PAUSA chefes por 1,6s — depois o chefe fica imune a esse agarrão por 8s.</t>
+          <t xml:space="preserve">Segura 5 inimigos por 5,5s cada, 19/s em cada um (95/s lotado). Também PAUSA chefes por 1,6s — depois o chefe fica imune a esse agarrão por 8s.</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passa a BLOQUEAR: segura até 4 comuns por 4s (elite ocupa 2 vagas; chefe não é preso, só cai para 60% da velocidade por 1,4s). Depois de soltar, 3s de recarga. Zona de turbulência de raio 150 px deixa quem passa a 80% da velocidade.</t>
+          <t xml:space="preserve">Segura até 4 comuns por 4s (elite ocupa 2 vagas; chefe não é preso, só cai para 60% da velocidade por 1,4s). Depois de soltar, 3s de recarga. V3.1: NÃO mexe mais na água — turbulência virou exclusividade do ramo Correnteza.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segura 6 comuns por 5s (chefe: 50% da velocidade por 1,6s). Zona de 150 px a 78%. Repulsa Ancestral a cada 9s: empurra comuns 110 px rota abaixo, elites 66 px (60%), chefes só levam o slow.</t>
+          <t xml:space="preserve">Segura 6 comuns por 5s (chefe: 50% da velocidade por 1,6s). Repulsa Ancestral a cada 9s: empurra comuns 110 px rota abaixo, elites 66 px (60%), chefes só levam o slow. Sem turbulência: isso é do outro ramo.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zona de corrente contrária de raio 180 px: TODOS os inimigos dentro andam a 62% da velocidade, sem recarga e sem limite de alvos.</t>
+          <t xml:space="preserve">Zona de corrente contrária de raio 180 px: TODOS os inimigos dentro andam a 62% da velocidade. V3.1: também SEGURA 3 inimigos por 3s.</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zona de raio 190 px a 55% da velocidade. A cada 9s uma corrente forte empurra comuns 170 px para trás na rota (elites 102 px); chefes recebem 45% de velocidade por 2s.</t>
+          <t xml:space="preserve">Zona de raio 190 px a 55% da velocidade. Segura 5 inimigos por 3,5s. A cada 9s uma corrente forte empurra comuns 170 px para trás na rota (elites 102 px); chefes recebem 45% de velocidade por 2s.</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">V3: ao primeiro contato abre uma janela de 0,5s — se 2 inimigos entrarem, explode na hora; se ninguém mais vier, explode no primeiro. 96 de dano, 1,6s de stun (elite 0,96s, chefe 0,4s) e empurra 90 px rota abaixo (elite 45 px). Com carga cheia o stun chega a 2,18s.</t>
+          <t xml:space="preserve">96 de dano, 1,6s de stun (elite 0,96s, chefe 0,4s) e empurra 90 px rota abaixo (elite 45 px). Com carga cheia o stun chega a 2,18s.</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recompensa GARANTIDA (não é sorteio): o jogador escolhe uma unidade em campo e a coroa. Amplifica o que o ramo dela já faz; alvo de 20% a 30% de ganho efetivo. A escolha vale só aquela partida e não tem volta.</t>
+          <t xml:space="preserve">Recompensa GARANTIDA (não é sorteio). V3.1: ele aparece nadando no canto inferior direito e o jogador ARRASTA até o Guardião que quer coroar — soltar no vazio traz ele de volta. Os benefícios estão ligados: ver a aba Peixinho Dourado. A escolha vale só aquela partida e não tem volta.</t>
         </is>
       </c>
     </row>

--- a/docs/balanceamento.xlsx
+++ b/docs/balanceamento.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">V3.1: bloqueia desde a base — 2 inimigos por 3s. A batida deixa o alvo a 75% da velocidade por 1,4s.</t>
+          <t xml:space="preserve">V3.1: bloqueia desde a base — 2 inimigos por 9s — 2,5x mais que o Baiacu: ela SEGURA, ele belisca. A batida deixa o alvo a 75% da velocidade por 1,4s.</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segura até 4 comuns por 4s (elite ocupa 2 vagas; chefe não é preso, só cai para 60% da velocidade por 1,4s). Depois de soltar, 3s de recarga. V3.1: NÃO mexe mais na água — turbulência virou exclusividade do ramo Correnteza.</t>
+          <t xml:space="preserve">Segura até 4 comuns por 12s (elite ocupa 2 vagas; chefe não é preso, só cai para 60% da velocidade por 1,4s). Depois de soltar, 3s de recarga. V3.1: NÃO mexe mais na água — turbulência virou exclusividade do ramo Correnteza.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segura 6 comuns por 5s (chefe: 50% da velocidade por 1,6s). Repulsa Ancestral a cada 9s: empurra comuns 110 px rota abaixo, elites 66 px (60%), chefes só levam o slow. Sem turbulência: isso é do outro ramo.</t>
+          <t xml:space="preserve">Segura 6 comuns por 14s (chefe: 50% da velocidade por 1,6s). Repulsa Ancestral a cada 9s: empurra comuns 110 px rota abaixo, elites 66 px (60%), chefes só levam o slow. Sem turbulência: isso é do outro ramo.</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zona de corrente contrária de raio 180 px: TODOS os inimigos dentro andam a 62% da velocidade. V3.1: também SEGURA 3 inimigos por 3s.</t>
+          <t xml:space="preserve">Zona de corrente contrária de raio 180 px: TODOS os inimigos dentro andam a 62% da velocidade. V3.1: também SEGURA 3 inimigos por 10s.</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zona de raio 190 px a 55% da velocidade. Segura 5 inimigos por 3,5s. A cada 9s uma corrente forte empurra comuns 170 px para trás na rota (elites 102 px); chefes recebem 45% de velocidade por 2s.</t>
+          <t xml:space="preserve">Zona de raio 190 px a 55% da velocidade. Segura 5 inimigos por 11s. A cada 9s uma corrente forte empurra comuns 170 px para trás na rota (elites 102 px); chefes recebem 45% de velocidade por 2s.</t>
         </is>
       </c>
     </row>

--- a/docs/balanceamento.xlsx
+++ b/docs/balanceamento.xlsx
@@ -576,32 +576,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadilha</t>
+          <t xml:space="preserve">Emboscada • Veneno</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correnteza (rota)</t>
+          <t xml:space="preserve">Borda da correnteza</t>
         </is>
       </c>
       <c r="E9">
         <v>95</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>16</v>
+        <v>27.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armadilha (não usa a FSM de ataque)</t>
+          <t xml:space="preserve">Emboscada (não usa a FSM de ataque)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">V3.1: NÃO dispara no primeiro contato. Enterra-se em 2,6s e espera o grupo se formar, saindo pouco antes de o primeiro escapar do raio 65 (a 53 px dela) — o instante com mais gente dentro. 40 de dano, recarga 2,5s (era 5s). Cada 2s armado soma +6% (teto +36% = 54,4).</t>
+          <t xml:space="preserve">V3.2 — DEIXOU DE SER ARMADILHA DESCARTÁVEL. Encaixa na BORDA da correnteza, camuflado de pedra, com a zona (raio 70) invadindo a rota. Quando alguém entra, abre os espinhos em 0,42s e dá o bote: 46 em área + veneno de 9/s por 4s (até 2 acúmulos = 72). Recolhe, recarrega 3s e repete a partida inteira. O bote é COMPROMETIDO: sai mesmo que o alvo escape no meio da abertura — é o que separa uma emboscada de um tiro teleguiado. Só a primeira camuflagem custa tempo (1,6s); depois o ciclo nunca mais se enterra do zero.</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arma mais rápido e explode mais forte</t>
+          <t xml:space="preserve">Bote +20%, zona +12%, recarga −15%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mais resíduo tóxico no lugar</t>
+          <t xml:space="preserve">Bote +15%, zona +12%, veneno 20% mais longo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mais choque ou repulsa mais larga</t>
+          <t xml:space="preserve">Bote +25%, recarga −18%, zona +8%</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1120,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peixe-Pedra B2: leitura da janela</t>
+          <t xml:space="preserve">Peixe-Pedra: calibrar o ciclo novo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementei a leitura literal: o segundo inimigo dentro da janela de 0,5s detona na hora.</t>
+          <t xml:space="preserve">A V3.2 trocou a armadilha de uso único pelo emboscador recorrente: 3s de recarga, bote comprometido e zona na borda da correnteza. Os números passaram na simulação, mas nunca foram jogados à mão.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmar se é isso mesmo, ou se deveria esperar a janela inteira e pegar todos.</t>
+          <t xml:space="preserve">Ver se 3s de recarga não o deixa forte demais em rota estreita, e se a zona de 54 do ramo B não é pequena demais para acertar alguém.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veneno</t>
+          <t xml:space="preserve">Jardim Tóxico</t>
         </is>
       </c>
       <c r="D30">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Espinhos Tóxicos</t>
+          <t xml:space="preserve">Toxina Viva</t>
         </is>
       </c>
       <c r="F30">
@@ -2623,21 +2623,21 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 + veneno</t>
+          <t xml:space="preserve">40 + veneno + névoa</t>
         </is>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>15.8</v>
+        <v>30</v>
       </c>
       <c r="K30">
-        <v>24.8</v>
+        <v>46.7</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 no impacto + veneno de 9 de dano/s por 5s (45 de dano total). Acumula até 2× = 90 de veneno. Total por armadilha: 79 (124 com 2 acúmulos). A carga de espera (+6% a cada 2s, teto +36%) soma no DANO.</t>
+          <t xml:space="preserve">Zona sobe para 78. Bote de 40 + veneno de 10/s por 5s (50 por acúmulo, até 2× = 100). O bote deixa no chão uma NÉVOA de raio 88 por 4s: quem atravessa é envenenado (8/s por 4s = 32) e anda a 85% da velocidade. O custo da névoa não sobe com o nº de alvos — ela cobra o mesmo de todo mundo que passa.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veneno</t>
+          <t xml:space="preserve">Jardim Tóxico</t>
         </is>
       </c>
       <c r="D31">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jardim Tóxico</t>
+          <t xml:space="preserve">Jardim Abissal</t>
         </is>
       </c>
       <c r="F31">
@@ -2673,21 +2673,21 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 + veneno + nuvem</t>
+          <t xml:space="preserve">40 + veneno + névoa maior</t>
         </is>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>18.8</v>
+        <v>33.3</v>
       </c>
       <c r="K31">
-        <v>30.8</v>
+        <v>53.3</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 + veneno de 10/s por 6s (60 por acúmulo, até 2× = 120). Solta uma nuvem tóxica de raio 95 por 4,5s que envenena TODOS que passam com 8/s por 6s (48 cada).</t>
+          <t xml:space="preserve">Zona 86. Veneno de 10/s por 6s (60 por acúmulo, até 2× = 120). Névoa de raio 108 por 5s, agora a 80% da velocidade e envenenando 8/s por 6s (48). Quem MORRE envenenado dentro dela contamina os vizinhos num raio de 72 (8/s por 4s) — UMA vez por morte, sem reação em cadeia.</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emboscada</t>
+          <t xml:space="preserve">Predador de Emboscada</t>
         </is>
       </c>
       <c r="D32">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choque de Areia</t>
+          <t xml:space="preserve">Espinhos Cortantes</t>
         </is>
       </c>
       <c r="F32">
@@ -2721,23 +2721,25 @@
       <c r="G32">
         <v>175</v>
       </c>
-      <c r="H32">
-        <v>58</v>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82 + veneno</t>
+        </is>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J32">
-        <v>11.6</v>
+        <v>39.3</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">11,6/s × nº de alvos</t>
+          <t xml:space="preserve">Zona pequena: quase sempre 1 alvo</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emerge com 58 de dano em área e ATORDOA por 1,1s (elite 0,66s, chefe 0,33s). Aqui a carga de espera (+6% a cada 2s, teto +36%) aumenta a DURAÇÃO DO CONTROLE, não o dano: até 1,5s de stun.</t>
+          <t xml:space="preserve">A zona ENCOLHE para 54 e o bote sobe para 82 IGNORANDO ARMADURA, mais o veneno da base (9/s por 4s). Contra o Cascudo (armadura 9, −36%) isso vale 82 cheios em vez de 52. Troca área por punição.</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2756,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emboscada</t>
+          <t xml:space="preserve">Predador de Emboscada</t>
         </is>
       </c>
       <c r="D33">
@@ -2762,7 +2764,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fúria Abissal</t>
+          <t xml:space="preserve">Caçador da Corrente</t>
         </is>
       </c>
       <c r="F33">
@@ -2771,23 +2773,25 @@
       <c r="G33">
         <v>315</v>
       </c>
-      <c r="H33">
-        <v>96</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96 + veneno + % da vida do alvo</t>
+        </is>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J33">
-        <v>19.2</v>
+        <v>44</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">19,2/s × nº de alvos</t>
+          <t xml:space="preserve">Zona pequena: quase sempre 1 alvo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">96 de dano, 1,6s de stun (elite 0,96s, chefe 0,4s) e empurra 90 px rota abaixo (elite 45 px). Com carga cheia o stun chega a 2,18s.</t>
+          <t xml:space="preserve">96 ignorando armadura + veneno. Quando um alvo FORTE (vida máxima ≥ 150) entra na zona ele TRAVA a presa, carrega os espinhos em 0,24s em vez de 0,42s e cobra pela vida MÁXIMA dela: +10% dessa vida, teto +80. Contra um comum de 90 o bônus é ruído; contra um Cascudo (210) são +21; contra o Quebra-Marés (469) o teto segura em +80 — punição real sem virar execução.</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3432,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2 Jardim Tóxico</t>
+          <t xml:space="preserve">A2 Jardim Abissal</t>
         </is>
       </c>
       <c r="C17">
         <v>315</v>
       </c>
       <c r="D17">
-        <v>18.8</v>
+        <v>33.3</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>10.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3454,21 +3458,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2 Fúria Abissal</t>
+          <t xml:space="preserve">B2 Caçador da Corrente</t>
         </is>
       </c>
       <c r="C18">
         <v>315</v>
       </c>
       <c r="D18">
-        <v>19.2</v>
+        <v>44</v>
       </c>
       <c r="E18">
-        <v>6.1</v>
+        <v>14</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Explosão de 96 + 1,6s de stun em grupo</t>
+          <t xml:space="preserve">Anti-elite: ignora armadura e cobra +10% da vida máxima do alvo (teto +80)</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6342,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areia Solta</t>
+          <t xml:space="preserve">Bote Rápido</t>
         </is>
       </c>
       <c r="D37">
@@ -6346,7 +6350,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">−4% no tempo de armação</t>
+          <t xml:space="preserve">−4% no tempo de abrir os espinhos</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rearme Rápido</t>
+          <t xml:space="preserve">Fôlego Curto</t>
         </is>
       </c>
       <c r="D38">
@@ -6369,7 +6373,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">−4% na recarga</t>
+          <t xml:space="preserve">−4% na recarga entre emboscadas</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6396,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">+4% no raio</t>
+          <t xml:space="preserve">+4% na zona de emboscada</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paciência Fria</t>
+          <t xml:space="preserve">Peçonha Densa</t>
         </is>
       </c>
       <c r="D40">
@@ -6415,7 +6419,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3 p.p. no teto da carga (+36% → +39%)</t>
+          <t xml:space="preserve">+4% na duração do veneno que ele aplica</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V3.2: substituiu o teto da carga, que não existe mais</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6447,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2: mais resíduo · B2: choque ou repulsa leve extra</t>
+          <t xml:space="preserve">A2 Ecossistema Tóxico: a PRIMEIRA entrada de cada inimigo no Jardim leva dose extra e curta · B2 Paciência Mortal: cada segundo camuflado sem atacar soma dano ao próximo bote, até um teto</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">

--- a/docs/balanceamento.xlsx
+++ b/docs/balanceamento.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">V3.2 — DEIXOU DE SER ARMADILHA DESCARTÁVEL. Encaixa na BORDA da correnteza, camuflado de pedra, com a zona (raio 70) invadindo a rota. Quando alguém entra, abre os espinhos em 0,42s e dá o bote: 46 em área + veneno de 9/s por 4s (até 2 acúmulos = 72). Recolhe, recarrega 3s e repete a partida inteira. O bote é COMPROMETIDO: sai mesmo que o alvo escape no meio da abertura — é o que separa uma emboscada de um tiro teleguiado. Só a primeira camuflagem custa tempo (1,6s); depois o ciclo nunca mais se enterra do zero.</t>
+          <t xml:space="preserve">V3.3: recarga 3s → 4,5s. V3.2 — DEIXOU DE SER ARMADILHA DESCARTÁVEL. Encaixa na BORDA da correnteza, camuflado de pedra, com a zona (raio 70) invadindo a rota. Quando alguém entra, abre os espinhos em 0,42s e dá o bote: 46 em área + veneno de 9/s por 4s (até 2 acúmulos = 72). Recolhe, recarrega 4,5s e repete a partida inteira. O bote é COMPROMETIDO: sai mesmo que o alvo escape no meio da abertura — é o que separa uma emboscada de um tiro teleguiado. Só a primeira camuflagem custa tempo (1,6s); depois o ciclo nunca mais se enterra do zero.</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">A V3.2 trocou a armadilha de uso único pelo emboscador recorrente: 3s de recarga, bote comprometido e zona na borda da correnteza. Os números passaram na simulação, mas nunca foram jogados à mão.</t>
+          <t xml:space="preserve">A V3.3 subiu a recarga de 3s para 4,5s, a pedido: a 3s ele emboscava quase sem parar e a fantasia de emboscador caía. Na simulação o efeito foi pequeno — a mesma partida do golden terminou 3,3s mais tarde, com as mesmas vidas e pérolas.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver se 3s de recarga não o deixa forte demais em rota estreita, e se a zona de 54 do ramo B não é pequena demais para acertar alguém.</t>
+          <t xml:space="preserve">Ver à mão se 4,5s deixa a espera boa sem tirar a relevância dele nas fases longas.</t>
         </is>
       </c>
     </row>

--- a/docs/balanceamento.xlsx
+++ b/docs/balanceamento.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">V3.3: recarga 3s → 4,5s. V3.2 — DEIXOU DE SER ARMADILHA DESCARTÁVEL. Encaixa na BORDA da correnteza, camuflado de pedra, com a zona (raio 70) invadindo a rota. Quando alguém entra, abre os espinhos em 0,42s e dá o bote: 46 em área + veneno de 9/s por 4s (até 2 acúmulos = 72). Recolhe, recarrega 4,5s e repete a partida inteira. O bote é COMPROMETIDO: sai mesmo que o alvo escape no meio da abertura — é o que separa uma emboscada de um tiro teleguiado. Só a primeira camuflagem custa tempo (1,6s); depois o ciclo nunca mais se enterra do zero.</t>
+          <t xml:space="preserve">V3.4: recarga 3s → 4,5s → 7s — ele deixou de ser fonte de dano por segundo e virou punição pontual. V3.2 — DEIXOU DE SER ARMADILHA DESCARTÁVEL. Encaixa na BORDA da correnteza, camuflado de pedra, com a zona (raio 70) invadindo a rota. Quando alguém entra, abre os espinhos em 0,42s e dá o bote: 46 em área + veneno de 9/s por 4s (até 2 acúmulos = 72). Recolhe, recarrega 7s e repete a partida inteira. O bote é COMPROMETIDO: sai mesmo que o alvo escape no meio da abertura — é o que separa uma emboscada de um tiro teleguiado. Só a primeira camuflagem custa tempo (1,6s); depois o ciclo nunca mais se enterra do zero.</t>
         </is>
       </c>
     </row>
